--- a/sample-project2/srcs/Access/build/test-results/reports/report-numeric.xlsx
+++ b/sample-project2/srcs/Access/build/test-results/reports/report-numeric.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\開発\contextbase-evaluation\sample-project2\srcs\Access\.tmp\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{05096716-3957-48EB-8868-99269F7C87A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F862D79F-7658-45CC-BC44-54693AEAD4B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1A5BC225-EEC7-4803-B6AE-80CA100B3A3A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{BCB19BAE-12D2-4866-AF5D-9CC7D56CF47E}"/>
   </bookViews>
   <sheets>
     <sheet name="職務経歴書" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
     <t>2026年10月30日現在</t>
   </si>
   <si>
-    <t>作成日時（JST）：2026年10月30日 01:44</t>
+    <t>作成日時（JST）：2026年10月30日 11:35</t>
   </si>
   <si>
     <t>氏名</t>
@@ -886,7 +886,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{904B5C2A-C0A0-46A7-95D7-D020982BCCAE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E77C54A-E336-4BAD-A6BD-4FED72DF78AA}">
   <dimension ref="A1:X46"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1"/>
   <cols>
@@ -2242,7 +2242,7 @@
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter scaleWithDoc="0">
     <oddFooter>&amp;C&amp;11&amp;"メイリオ,Regular"1234&amp;&amp;界界界界界界界界界界界界界界界界界界界界界界界界界界界界界界界界界界界
-職務経歴書 ／ 作成JST 2026年10月30日 01:44  &amp;P/&amp;N</oddFooter>
+職務経歴書 ／ 作成JST 2026年10月30日 11:35  &amp;P/&amp;N</oddFooter>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="40" max="23" man="1"/>
@@ -2251,7 +2251,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B378728-D03A-43BD-8ED4-2DA4F627B099}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F7FBA9D-565C-410B-9351-C7713679BAC6}">
   <dimension ref="A1:X56"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1"/>
   <cols>
@@ -4047,7 +4047,7 @@
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter scaleWithDoc="0">
     <oddFooter>&amp;C&amp;11&amp;"メイリオ,Regular"1234&amp;&amp;界界界界界界界界界界界界界界界界界界界界界界界界界界界界界界界界界界界
-案件経歴 ／ 作成JST 2026年10月30日 01:44  &amp;P/&amp;N</oddFooter>
+案件経歴 ／ 作成JST 2026年10月30日 11:35  &amp;P/&amp;N</oddFooter>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="38" max="23" man="1"/>
